--- a/docs/analisis-requisitos/HU-CPA-3200-ACCESO-PARTE-PUBLICA-LISTADO-CPA-CPA-VIRTUAL_V0.xlsx
+++ b/docs/analisis-requisitos/HU-CPA-3200-ACCESO-PARTE-PUBLICA-LISTADO-CPA-CPA-VIRTUAL_V0.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_CPA_Virtual\HU\SP1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_CPA_Virtual\HU\SP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7AFB59-584E-4036-AF48-6AB5C79533CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C345A3D-4E4D-4D37-A76B-515608034F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="204" xr2:uid="{611E275B-AF68-4D54-8B4F-28D93EBAB353}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="61">
   <si>
     <t>Enunciado de la historia</t>
   </si>
@@ -86,9 +86,6 @@
     <t>Campo check. Editable. No obligatorio.</t>
   </si>
   <si>
-    <t>Se presenta en el formulario el botón Buscar</t>
-  </si>
-  <si>
     <t>Si se decide pulsar el enlace.</t>
   </si>
   <si>
@@ -125,15 +122,9 @@
     <t>Formulario Listado CPA Parte Pública CPA Virtual</t>
   </si>
   <si>
-    <t>Introduce código postal, localidad o nombre</t>
-  </si>
-  <si>
     <t>Se presentará en el campo del formulario el valor introducido manualmente por el usuario.</t>
   </si>
   <si>
-    <t xml:space="preserve">Botón Lupa </t>
-  </si>
-  <si>
     <t>Detallado en la HU-CPA-4500-ACCESO-PARTE-PUBLICA-CPA-CPA-VIRTUAL_V0</t>
   </si>
   <si>
@@ -149,9 +140,6 @@
     <t>Listado CPAs</t>
   </si>
   <si>
-    <t>Se presenta un campo texto. Editable. No obligatorio. Por defecto sin contenido. Código postal, localidad y/o nombre de los distintos CPAs como criterios de búsqueda.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Acceso a todos los usuarios de la parte pública de CPA Virtual, desde dónde poder consultar la relación de CPAs coincidentes con la búsqueda realizada previamente mediante código portal, localidad o nombre de CPA. </t>
   </si>
   <si>
@@ -162,6 +150,64 @@
   </si>
   <si>
     <t>Cada uno de los CPAs, presentará un código, nombre, provincia y código postal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se presentará información relacionada con los CPAs, en base al criterio de búsqueda realizado previamente por el usuario.
+</t>
+  </si>
+  <si>
+    <t>Botón Aplicar</t>
+  </si>
+  <si>
+    <t>Se presenta en el formulario el botón Aplicar</t>
+  </si>
+  <si>
+    <t>código centro</t>
+  </si>
+  <si>
+    <t>nombre centro</t>
+  </si>
+  <si>
+    <t>código postal.</t>
+  </si>
+  <si>
+    <t>Campo texto. No editable</t>
+  </si>
+  <si>
+    <t>Se mostrará el valor obtenido previamente.</t>
+  </si>
+  <si>
+    <t>Si se selecciona un CPA del listado y se decide pulsar.</t>
+  </si>
+  <si>
+    <t>código provincia.</t>
+  </si>
+  <si>
+    <t>nombre provincia.</t>
+  </si>
+  <si>
+    <t>imagen centro</t>
+  </si>
+  <si>
+    <t>Campo multimedia. No editable.</t>
+  </si>
+  <si>
+    <t>código localidad.</t>
+  </si>
+  <si>
+    <t>nombre localidad.</t>
+  </si>
+  <si>
+    <t>código municipio</t>
+  </si>
+  <si>
+    <t>nombre municipio</t>
+  </si>
+  <si>
+    <t>nombre via</t>
+  </si>
+  <si>
+    <t>direccion</t>
   </si>
   <si>
     <r>
@@ -175,7 +221,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>ConsultaListadoCentrosporCPA'</t>
+      <t>ConsultaResultadoListadoCentros'</t>
     </r>
     <r>
       <rPr>
@@ -188,65 +234,17 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Mediante la operación '</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>consultaListadoCPAporCP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>' que accederá a los tipos de contenido 'UsuariosCentros', 'Centros', 'Localidades, 'Municipio', Provincias' del repositorio Drupal, se presentará en el formulario el listado de CPAs en base al filtro de búsqueda solicitado por el usuario.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Se presentará información relacionada con los CPAs, en base al criterio de búsqueda realizado previamente por el usuario.
-</t>
-  </si>
-  <si>
-    <t>Botón Aplicar</t>
-  </si>
-  <si>
-    <t>Se presenta en el formulario el botón Aplicar</t>
-  </si>
-  <si>
-    <t>código centro</t>
-  </si>
-  <si>
-    <t>nombre centro</t>
-  </si>
-  <si>
-    <t>provincia</t>
-  </si>
-  <si>
-    <t>código postal.</t>
-  </si>
-  <si>
-    <t>Campo texto. No editable</t>
-  </si>
-  <si>
-    <t>Se mostrará el valor obtenido previamente.</t>
-  </si>
-  <si>
-    <t>Si se selecciona un CPA del listado y se decide pulsar.</t>
+    <t>Introduce código postal, localidad, provincia o nombre</t>
+  </si>
+  <si>
+    <t>Se presenta un campo texto. Editable. No obligatorio. Por defecto sin contenido. Código postal, localidad, provincia y/o nombre de los distintos CPAs como criterios de búsqueda.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -256,13 +254,6 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -408,16 +399,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>120777</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>1744952</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71AC6453-6811-2688-B613-C5C6AC575CF2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F4E8C35-622D-C5BE-D486-696D4DADA025}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -434,7 +425,51 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="2476627" cy="3606800"/>
+          <a:ext cx="4100802" cy="5448300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>717645</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>63696</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17E75359-EA14-E037-A903-BD3D56AC56B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4737100" y="63500"/>
+          <a:ext cx="1854295" cy="3810196"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -801,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD33D8B-FAA8-4740-A39A-FB2519115401}">
-  <dimension ref="A24:I45"/>
+  <dimension ref="A36:I64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.7265625" customWidth="1"/>
@@ -814,469 +849,600 @@
     <col min="9" max="9" width="40.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="24" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+    <row r="36" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="4" t="s">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-    </row>
-    <row r="25" spans="1:9" ht="29" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+    </row>
+    <row r="37" spans="1:9" ht="29" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+    <row r="38" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="C38" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="G38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="2">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="2">
-        <v>2</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="88" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="2">
-        <v>3</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="25" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="2">
-        <v>4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="25" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="2">
-        <v>5</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="25" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="2">
-        <v>6</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="25" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="2">
-        <v>7</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="25" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="2">
-        <v>8</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="25" x14ac:dyDescent="0.25">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="2">
-        <v>9</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="25" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="2">
-        <v>10</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="25" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="2">
-        <v>11</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="25" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="2">
-        <v>12</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="163" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="2">
-        <v>13</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
-      <c r="E39" s="2"/>
+      <c r="E39" s="2">
+        <v>2</v>
+      </c>
       <c r="F39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-    </row>
-    <row r="40" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="25" x14ac:dyDescent="0.25">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="2">
+        <v>4</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="H40" s="3" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="25" x14ac:dyDescent="0.25">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="2"/>
+      <c r="E41" s="2">
+        <v>5</v>
+      </c>
       <c r="F41" s="3" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="25" x14ac:dyDescent="0.25">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
-      <c r="E42" s="2"/>
+      <c r="E42" s="2">
+        <v>6</v>
+      </c>
       <c r="F42" s="3" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="25" x14ac:dyDescent="0.25">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="2"/>
+      <c r="E43" s="2">
+        <v>7</v>
+      </c>
       <c r="F43" s="3" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="25" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="2"/>
+      <c r="E44" s="2">
+        <v>8</v>
+      </c>
       <c r="F44" s="3" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="25" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="2">
+        <v>9</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F45" s="3" t="s">
+    </row>
+    <row r="46" spans="1:9" ht="25" x14ac:dyDescent="0.25">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="2">
+        <v>10</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="25" x14ac:dyDescent="0.25">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="2">
+        <v>11</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="25" x14ac:dyDescent="0.25">
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="2">
+        <v>12</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="163" x14ac:dyDescent="0.25">
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="2">
+        <v>13</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>36</v>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+    </row>
+    <row r="51" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="2">
+        <v>14</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="7"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="7"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="7"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="7"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="7"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="7"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="2">
+        <v>15</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="4">
-    <mergeCell ref="A26:A45"/>
-    <mergeCell ref="B26:B45"/>
-    <mergeCell ref="C26:C45"/>
-    <mergeCell ref="D26:D45"/>
+    <mergeCell ref="A38:A64"/>
+    <mergeCell ref="B38:B64"/>
+    <mergeCell ref="C38:C64"/>
+    <mergeCell ref="D38:D64"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
